--- a/04_DESIGN_TABLES/DesignTable_1603_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1603_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY6"/>
+  <dimension ref="A1:CY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1930,293 +1930,293 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1603-12-12-12-FG</t>
+          <t>1603-08-08-08-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="C5" t="n">
-        <v>0.531</v>
+        <v>0.4375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="E5" t="n">
-        <v>0.389</v>
+        <v>0.304</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745</v>
+        <v>0.72</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5694</v>
+        <v>0.455</v>
       </c>
       <c r="H5" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
         <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="L5" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="M5" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="N5" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="O5" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5625</v>
+        <v>0.4425</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6189</v>
+        <v>0.595</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4635</v>
+        <v>0.37</v>
       </c>
       <c r="S5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="T5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>0.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>0.531</v>
+        <v>0.4375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.389</v>
+        <v>0.304</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.745</v>
+        <v>0.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5694</v>
+        <v>0.455</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AE5" t="n">
         <v>0.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5625</v>
+        <v>0.4425</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6189</v>
+        <v>0.595</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.4635</v>
+        <v>0.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.531</v>
+        <v>0.4375</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.389</v>
+        <v>0.304</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.745</v>
+        <v>0.72</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.5694</v>
+        <v>0.455</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.5625</v>
+        <v>0.4425</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.6189</v>
+        <v>0.595</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.4635</v>
+        <v>0.37</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
         <v>0.4</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="BR5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.97</v>
+        <v>0.759</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.393</v>
+        <v>0.388</v>
       </c>
       <c r="BU5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.54214</v>
+        <v>0.43664</v>
       </c>
       <c r="BX5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.97</v>
+        <v>0.759</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.393</v>
+        <v>0.388</v>
       </c>
       <c r="CA5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.54214</v>
+        <v>0.43664</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.97</v>
+        <v>0.759</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.393</v>
+        <v>0.388</v>
       </c>
       <c r="CG5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.54214</v>
+        <v>0.43664</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.062</v>
+        <v>0.875</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.062</v>
+        <v>0.875</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>1603-12-12-12-FG</t>
+          <t>1603-08-08-08-FG</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>Female NPSM Swivel Tee (three swivels), 3/4-14 NPSM (female swivel) x 3/4-14 NPSM (female swivel) x 3/4-14 NPSM (female swivel)</t>
+          <t>Female NPSM Swivel Tee (three swivels), 1/2-14 NPSM (female swivel) x 1/2-14 NPSM (female swivel) x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
@@ -2226,17 +2226,17 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
@@ -2246,348 +2246,681 @@
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex C1HEX (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (1404 straight body face BODY_TO_TIP; on a tee seen on the Brennan 1601-08-08-08-FG / 1603-08-08-08-FG tee forgings - shape only, every NPSM swivel there = NPSM_MEAS[8]); NUT FACE AT THE ROW W5_2 / W5_3 / W3 AND STEM TIP AT THE ROW M2_2 / M2_3 / M1 (crossing to the nut face / to the stem tip, per leg) (the row is followed; its nut face to stem tip is compared with the Brennan 1404 value TIP_B per row, a difference is said in $COMMENT); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing; 1603 side order: part-number side 1 (W3 / M1) = the branch leg, sides 2 / 3 (W5 / M2) = the run (ASSUMPTION: Air-Way prints side 1 differently, the Brennan TFA 1603 table labels A1 as the branch; every -FG row has equal dashes)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); D1 / D2 bores measured on BRENNAN_1603-08-08-08-FG.stp 2026-10-20 (A14); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex C1HEX (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (1404 straight body face BODY_TO_TIP; on a tee seen on the Brennan 1601-08-08-08-FG / 1603-08-08-08-FG tee forgings - shape only, every NPSM swivel there = NPSM_MEAS[8]); NUT FACE AT THE ROW W5_2 / W5_3 / W3 AND STEM TIP AT THE ROW M2_2 / M2_3 / M1 (crossing to the nut face / to the stem tip, per leg) (the row is followed; its nut face to stem tip is compared with the Brennan 1404 value TIP_B per row, a difference is said in $COMMENT); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing; 1603 side order: part-number side 1 (W3 / M1) = the branch leg, sides 2 / 3 (W5 / M2) = the run (ASSUMPTION: Air-Way prints side 1 differently, the Brennan TFA 1603 table labels A1 as the branch; every -FG row has equal dashes)</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: nut face to stem tip 0.350 (row) vs 0.330 on the Brennan -12 swivel (TIP_B) - the row is followed; leg 2: nut face to stem tip 0.350 (row) vs 0.330 on the Brennan -12 swivel (TIP_B) - the row is followed; leg 3: nut face to stem tip 0.350 (row) vs 0.330 on the Brennan -12 swivel (TIP_B) - the row is followed</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | 2026-10-20 A14: D1 / D2 bores 0.450 measured on the Brennan STEP (catalog prints the range 0.44/0.46); the other sizes = the Brennan TFA catalog p.48, all confirmed on the same STEP (nut faces 1.39, stem tips 1.11, nut hex 1.000, body flats 0.875) - staged, not shipped</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>1603-12-12-12-FG</t>
+          <t>1603-08-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1603-16-16-16-FG</t>
+          <t>1603-12-12-12-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="C6" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.525</v>
+        <v>0.389</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7098</v>
+        <v>0.5694</v>
       </c>
       <c r="H6" t="n">
-        <v>0.175</v>
+        <v>0.135</v>
       </c>
       <c r="I6" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="N6" t="n">
-        <v>0.428</v>
+        <v>0.361</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="P6" t="n">
-        <v>0.67</v>
+        <v>0.5625</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7447</v>
+        <v>0.6189</v>
       </c>
       <c r="R6" t="n">
-        <v>0.59</v>
+        <v>0.4635</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4845</v>
+        <v>0.375</v>
       </c>
       <c r="T6" t="n">
         <v>0.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.525</v>
+        <v>0.389</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.9</v>
+        <v>0.745</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7098</v>
+        <v>0.5694</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.175</v>
+        <v>0.135</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.428</v>
+        <v>0.361</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.67</v>
+        <v>0.5625</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7447</v>
+        <v>0.6189</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.59</v>
+        <v>0.4635</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.4845</v>
+        <v>0.375</v>
       </c>
       <c r="AO6" t="n">
         <v>0.35</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.525</v>
+        <v>0.389</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.9</v>
+        <v>0.745</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.7098</v>
+        <v>0.5694</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.175</v>
+        <v>0.135</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.428</v>
+        <v>0.361</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.67</v>
+        <v>0.5625</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.7447</v>
+        <v>0.6189</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.59</v>
+        <v>0.4635</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.4845</v>
+        <v>0.375</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.35</v>
       </c>
       <c r="BK6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>1603-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>Female NPSM Swivel Tee (three swivels), 3/4-14 NPSM (female swivel) x 3/4-14 NPSM (female swivel) x 3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex C1HEX (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (1404 straight body face BODY_TO_TIP; on a tee seen on the Brennan 1601-08-08-08-FG / 1603-08-08-08-FG tee forgings - shape only, every NPSM swivel there = NPSM_MEAS[8]); NUT FACE AT THE ROW W5_2 / W5_3 / W3 AND STEM TIP AT THE ROW M2_2 / M2_3 / M1 (crossing to the nut face / to the stem tip, per leg) (the row is followed; its nut face to stem tip is compared with the Brennan 1404 value TIP_B per row, a difference is said in $COMMENT); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing; 1603 side order: part-number side 1 (W3 / M1) = the branch leg, sides 2 / 3 (W5 / M2) = the run (ASSUMPTION: Air-Way prints side 1 differently, the Brennan TFA 1603 table labels A1 as the branch; every -FG row has equal dashes)</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: nut face to stem tip 0.350 (row) vs 0.330 on the Brennan -12 swivel (TIP_B) - the row is followed; leg 2: nut face to stem tip 0.350 (row) vs 0.330 on the Brennan -12 swivel (TIP_B) - the row is followed; leg 3: nut face to stem tip 0.350 (row) vs 0.330 on the Brennan -12 swivel (TIP_B) - the row is followed</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>1603-12-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1603-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="V7" t="n">
         <v>0.5</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="W7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0.78</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BN7" t="n">
         <v>1.89</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BO7" t="n">
         <v>0.78</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BP7" t="n">
         <v>1.89</v>
       </c>
-      <c r="BQ6" t="n">
+      <c r="BQ7" t="n">
         <v>0.78</v>
       </c>
-      <c r="BR6" t="n">
+      <c r="BR7" t="n">
         <v>1.89</v>
       </c>
-      <c r="BS6" t="n">
+      <c r="BS7" t="n">
         <v>1.211</v>
       </c>
-      <c r="BT6" t="n">
+      <c r="BT7" t="n">
         <v>0.469</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="BU7" t="n">
         <v>0.08696</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="BV7" t="n">
         <v>0.6055</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="BW7" t="n">
         <v>0.6750699999999999</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="BX7" t="n">
         <v>1.89</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="BY7" t="n">
         <v>1.211</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="BZ7" t="n">
         <v>0.469</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CA7" t="n">
         <v>0.08696</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CB7" t="n">
         <v>0.6055</v>
       </c>
-      <c r="CC6" t="n">
+      <c r="CC7" t="n">
         <v>0.6750699999999999</v>
       </c>
-      <c r="CD6" t="n">
+      <c r="CD7" t="n">
         <v>1.89</v>
       </c>
-      <c r="CE6" t="n">
+      <c r="CE7" t="n">
         <v>1.211</v>
       </c>
-      <c r="CF6" t="n">
+      <c r="CF7" t="n">
         <v>0.469</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CG7" t="n">
         <v>0.08696</v>
       </c>
-      <c r="CH6" t="n">
+      <c r="CH7" t="n">
         <v>0.6055</v>
       </c>
-      <c r="CI6" t="n">
+      <c r="CI7" t="n">
         <v>0.6750699999999999</v>
       </c>
-      <c r="CJ6" t="n">
+      <c r="CJ7" t="n">
         <v>1.89</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="CK7" t="n">
         <v>1.312</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CL7" t="n">
         <v>0.95</v>
       </c>
-      <c r="CM6" t="n">
+      <c r="CM7" t="n">
         <v>0.95</v>
       </c>
-      <c r="CN6" t="n">
+      <c r="CN7" t="n">
         <v>1.312</v>
       </c>
-      <c r="CO6" t="n">
+      <c r="CO7" t="n">
         <v>0.95</v>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>1603-16-16-16-FG</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>Female NPSM Swivel Tee (three swivels), 1-11 1/2 NPSM (female swivel) x 1-11 1/2 NPSM (female swivel) x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>1603</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex C1HEX (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (1404 straight body face BODY_TO_TIP; on a tee seen on the Brennan 1601-08-08-08-FG / 1603-08-08-08-FG tee forgings - shape only, every NPSM swivel there = NPSM_MEAS[8]); NUT FACE AT THE ROW W5_2 / W5_3 / W3 AND STEM TIP AT THE ROW M2_2 / M2_3 / M1 (crossing to the nut face / to the stem tip, per leg) (the row is followed; its nut face to stem tip is compared with the Brennan 1404 value TIP_B per row, a difference is said in $COMMENT); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing; 1603 side order: part-number side 1 (W3 / M1) = the branch leg, sides 2 / 3 (W5 / M2) = the run (ASSUMPTION: Air-Way prints side 1 differently, the Brennan TFA 1603 table labels A1 as the branch; every -FG row has equal dashes)</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>1603-16-16-16-FG</t>
         </is>
